--- a/data/trans_camb/P20-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P20-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,0</t>
+          <t>1,38; 9,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,12</t>
+          <t>-1,64; 5,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,26</t>
+          <t>-2,88; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,15</t>
+          <t>3,08; 13,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 11,57</t>
+          <t>1,71; 11,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,74</t>
+          <t>-2,65; 4,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,66</t>
+          <t>3,35; 9,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,3</t>
+          <t>1,42; 7,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,34</t>
+          <t>-1,58; 3,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 420,4</t>
+          <t>12,97; 427,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 229,95</t>
+          <t>-37,3; 217,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 150,32</t>
+          <t>-55,36; 151,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,69; 435,62</t>
+          <t>35,17; 487,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,32; 404,16</t>
+          <t>17,0; 407,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 172,55</t>
+          <t>-36,58; 170,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,98; 345,87</t>
+          <t>51,17; 303,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,58; 249,5</t>
+          <t>24,36; 224,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 114,31</t>
+          <t>-27,96; 105,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,48</t>
+          <t>0,18; 6,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,47</t>
+          <t>-3,79; 1,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,39</t>
+          <t>-0,92; 5,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,86</t>
+          <t>-1,63; 6,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,85</t>
+          <t>-6,04; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -2,03</t>
+          <t>-8,51; -2,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,38</t>
+          <t>0,16; 5,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,3</t>
+          <t>-4,02; 0,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,76</t>
+          <t>-3,65; 0,72</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 171,99</t>
+          <t>0,1; 183,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,43; 43,67</t>
+          <t>-57,47; 46,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 140,82</t>
+          <t>-17,46; 141,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 75,88</t>
+          <t>-14,9; 80,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 15,23</t>
+          <t>-53,17; 14,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; -24,51</t>
+          <t>-72,71; -27,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 87,7</t>
+          <t>0,93; 79,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 5,91</t>
+          <t>-47,38; 6,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 13,31</t>
+          <t>-43,08; 11,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 9,09</t>
+          <t>1,65; 8,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,91</t>
+          <t>-2,36; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,81</t>
+          <t>2,96; 10,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,92</t>
+          <t>1,52; 10,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 9,57</t>
+          <t>1,06; 8,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,2</t>
+          <t>1,09; 8,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,1</t>
+          <t>2,73; 8,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,49</t>
+          <t>0,35; 5,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,18</t>
+          <t>2,83; 7,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,81; 728,67</t>
+          <t>23,05; 819,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 298,47</t>
+          <t>-65,37; 275,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,96; 861,0</t>
+          <t>56,7; 945,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 304,68</t>
+          <t>21,54; 334,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,56; 278,63</t>
+          <t>13,66; 276,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 261,99</t>
+          <t>15,08; 264,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,18; 314,51</t>
+          <t>49,47; 315,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 222,34</t>
+          <t>6,07; 209,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,44; 312,3</t>
+          <t>52,44; 304,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,01</t>
+          <t>0,48; 6,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,19</t>
+          <t>2,5; 9,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,25</t>
+          <t>2,21; 10,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,47</t>
+          <t>0,84; 8,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 6,39</t>
+          <t>-0,72; 6,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,09</t>
+          <t>-2,13; 5,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,23</t>
+          <t>1,64; 6,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,69</t>
+          <t>1,86; 6,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,5</t>
+          <t>0,62; 6,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,16; 617,18</t>
+          <t>5,12; 544,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64,47; 845,26</t>
+          <t>70,76; 760,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62,09; 791,53</t>
+          <t>49,29; 766,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 227,86</t>
+          <t>9,15; 216,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 166,31</t>
+          <t>-11,8; 181,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 150,99</t>
+          <t>-34,92; 155,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,52; 236,36</t>
+          <t>34,72; 229,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,55; 238,38</t>
+          <t>35,35; 245,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,23; 210,37</t>
+          <t>12,12; 233,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 4,63</t>
+          <t>-4,98; 4,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,87</t>
+          <t>-6,61; 1,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,96</t>
+          <t>-8,06; -0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 6,52</t>
+          <t>-5,28; 6,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 1,07</t>
+          <t>-8,97; 1,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -1,32</t>
+          <t>-10,2; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,6</t>
+          <t>-3,29; 4,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,13</t>
+          <t>-6,22; 0,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -2,0</t>
+          <t>-7,48; -1,79</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 112,94</t>
+          <t>-58,51; 108,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,27; 65,98</t>
+          <t>-75,28; 53,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,69; -11,39</t>
+          <t>-86,84; -5,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 111,56</t>
+          <t>-43,36; 118,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 20,65</t>
+          <t>-76,59; 22,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,15; -14,25</t>
+          <t>-77,38; -14,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 58,11</t>
+          <t>-34,74; 71,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 5,45</t>
+          <t>-64,82; 10,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,32; -33,16</t>
+          <t>-74,16; -28,11</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,43</t>
+          <t>-1,84; 6,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,64</t>
+          <t>0,05; 7,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,3</t>
+          <t>1,44; 8,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 4,02</t>
+          <t>-6,44; 3,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 4,79</t>
+          <t>-6,12; 5,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 2,06</t>
+          <t>-7,88; 1,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,53</t>
+          <t>-2,88; 3,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,83</t>
+          <t>-1,83; 4,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,13</t>
+          <t>-1,76; 4,12</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 236,64</t>
+          <t>-39,74; 218,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 323,35</t>
+          <t>-10,47; 300,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22,38; 432,68</t>
+          <t>17,44; 364,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 54,47</t>
+          <t>-48,73; 43,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 59,65</t>
+          <t>-46,59; 57,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 26,12</t>
+          <t>-56,45; 23,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 60,43</t>
+          <t>-31,92; 53,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 86,6</t>
+          <t>-21,0; 80,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 77,88</t>
+          <t>-19,64; 71,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,6</t>
+          <t>-3,89; 1,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,88</t>
+          <t>-4,45; 0,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,57</t>
+          <t>-2,84; 2,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,05</t>
+          <t>-3,07; 3,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,8</t>
+          <t>-4,44; 1,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,75</t>
+          <t>-6,89; 0,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,41</t>
+          <t>-2,6; 1,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,33</t>
+          <t>-3,49; 0,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,76</t>
+          <t>-4,2; 0,71</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 39,65</t>
+          <t>-51,1; 27,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 22,14</t>
+          <t>-62,09; 12,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 59,24</t>
+          <t>-37,78; 55,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 47,18</t>
+          <t>-30,13; 49,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 26,15</t>
+          <t>-45,82; 24,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-70,29; 8,19</t>
+          <t>-66,54; 9,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 23,57</t>
+          <t>-31,19; 24,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 6,23</t>
+          <t>-42,18; 9,37</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 11,46</t>
+          <t>-51,14; 9,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,43</t>
+          <t>-0,79; 3,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,12</t>
+          <t>-0,8; 3,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,86</t>
+          <t>-3,2; 0,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,37</t>
+          <t>-1,67; 3,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,19</t>
+          <t>-3,03; 2,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,74; -0,33</t>
+          <t>-4,88; -0,31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,75</t>
+          <t>-0,52; 2,83</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,88</t>
+          <t>-1,24; 1,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -0,44</t>
+          <t>-3,56; -0,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 137,0</t>
+          <t>-19,55; 125,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 122,57</t>
+          <t>-20,71; 119,73</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-75,55; 29,06</t>
+          <t>-72,93; 27,68</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 65,68</t>
+          <t>-22,44; 74,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 47,76</t>
+          <t>-39,2; 40,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-59,19; -1,9</t>
+          <t>-61,08; -5,21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 67,03</t>
+          <t>-10,12; 67,11</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 46,1</t>
+          <t>-22,89; 45,8</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-63,43; -10,92</t>
+          <t>-61,77; -6,61</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,08</t>
+          <t>0,87; 3,07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,74</t>
+          <t>-0,37; 1,67</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,46</t>
+          <t>-0,13; 2,44</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,46</t>
+          <t>0,83; 3,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,71</t>
+          <t>-0,92; 1,56</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,18</t>
+          <t>-2,82; -0,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,92</t>
+          <t>1,08; 2,94</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,42</t>
+          <t>-0,34; 1,29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,79</t>
+          <t>-1,12; 0,8</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>18,03; 85,72</t>
+          <t>19,09; 86,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 47,99</t>
+          <t>-8,53; 45,19</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2,06; 66,53</t>
+          <t>-2,29; 66,86</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9,42; 51,69</t>
+          <t>10,13; 52,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 25,69</t>
+          <t>-11,09; 23,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-35,19; -2,68</t>
+          <t>-36,1; -2,96</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,84; 54,66</t>
+          <t>17,48; 55,9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 27,01</t>
+          <t>-5,43; 23,72</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 14,32</t>
+          <t>-18,15; 14,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P20-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,4</t>
+          <t>1,21; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,15</t>
+          <t>-1,75; 4,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,06</t>
+          <t>-3,31; 2,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,33</t>
+          <t>3,29; 12,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,88</t>
+          <t>2,2; 11,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,61</t>
+          <t>-1,74; 5,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,83</t>
+          <t>3,48; 9,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,02</t>
+          <t>1,33; 7,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,1</t>
+          <t>-1,41; 3,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>-0,82%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 427,8</t>
+          <t>14,62; 413,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 217,52</t>
+          <t>-38,24; 214,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 151,07</t>
+          <t>-58,62; 146,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,17; 487,64</t>
+          <t>42,12; 447,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 407,66</t>
+          <t>23,17; 409,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 170,75</t>
+          <t>-25,66; 195,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,17; 303,28</t>
+          <t>58,57; 323,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,36; 224,16</t>
+          <t>23,37; 231,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 105,08</t>
+          <t>-24,32; 115,03</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>-4,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 6,68</t>
+          <t>-0,03; 6,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,79</t>
+          <t>-3,8; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,72</t>
+          <t>-0,84; 5,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,2</t>
+          <t>-1,77; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 0,95</t>
+          <t>-6,2; 0,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -2,19</t>
+          <t>-7,82; -1,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,16</t>
+          <t>0,17; 5,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,44</t>
+          <t>-3,96; 0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,72</t>
+          <t>-3,64; 0,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-53,61%</t>
+          <t>-52,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-19,27%</t>
+          <t>-17,26%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 183,05</t>
+          <t>-1,74; 177,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 46,24</t>
+          <t>-57,41; 49,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 141,23</t>
+          <t>-13,39; 146,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 80,5</t>
+          <t>-16,65; 73,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 14,95</t>
+          <t>-52,59; 11,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,71; -27,17</t>
+          <t>-70,37; -23,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 79,31</t>
+          <t>1,22; 81,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 6,39</t>
+          <t>-47,12; 7,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 11,86</t>
+          <t>-43,09; 12,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,9</t>
+          <t>1,86; 8,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,89</t>
+          <t>-2,08; 2,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,07</t>
+          <t>2,88; 9,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 10,45</t>
+          <t>1,65; 9,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,96</t>
+          <t>1,02; 9,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 8,2</t>
+          <t>0,56; 7,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,41</t>
+          <t>2,93; 8,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,3</t>
+          <t>0,33; 5,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,74</t>
+          <t>2,71; 7,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271,27%</t>
+          <t>263,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>148,96%</t>
+          <t>145,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,05; 819,04</t>
+          <t>30,67; 778,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,37; 275,5</t>
+          <t>-62,71; 266,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56,7; 945,25</t>
+          <t>56,78; 943,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,54; 334,05</t>
+          <t>23,06; 313,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 276,64</t>
+          <t>9,15; 289,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,08; 264,45</t>
+          <t>7,52; 244,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,47; 315,18</t>
+          <t>55,94; 336,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 209,56</t>
+          <t>4,95; 210,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,44; 304,95</t>
+          <t>50,79; 299,53</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>4,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,13</t>
+          <t>0,69; 5,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,13</t>
+          <t>2,78; 9,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 10,01</t>
+          <t>2,54; 10,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,54</t>
+          <t>0,81; 8,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,79</t>
+          <t>-0,82; 6,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 5,8</t>
+          <t>0,11; 8,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,37</t>
+          <t>1,79; 6,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,73</t>
+          <t>1,88; 7,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,45</t>
+          <t>2,06; 7,82</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>259,66%</t>
+          <t>258,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>123,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 544,19</t>
+          <t>10,16; 519,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>70,76; 760,01</t>
+          <t>78,66; 789,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,29; 766,21</t>
+          <t>67,77; 817,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,15; 216,68</t>
+          <t>8,5; 232,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 181,87</t>
+          <t>-15,84; 179,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 155,0</t>
+          <t>-1,71; 227,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,72; 229,29</t>
+          <t>34,67; 234,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,35; 245,2</t>
+          <t>38,9; 253,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,12; 233,92</t>
+          <t>44,0; 275,88</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-4,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 4,59</t>
+          <t>-4,47; 4,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,69</t>
+          <t>-6,96; 1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -0,41</t>
+          <t>-8,31; -0,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 6,69</t>
+          <t>-5,04; 5,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 1,07</t>
+          <t>-9,72; 0,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,2; -0,88</t>
+          <t>-10,65; -1,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 4,18</t>
+          <t>-3,75; 3,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,45</t>
+          <t>-7,0; -0,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,48; -1,79</t>
+          <t>-7,82; -1,94</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-62,46%</t>
+          <t>-65,67%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-56,38%</t>
+          <t>-56,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-58,21%</t>
+          <t>-59,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,51; 108,66</t>
+          <t>-53,25; 120,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 53,35</t>
+          <t>-74,41; 52,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,84; -5,03</t>
+          <t>-85,93; -11,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 118,6</t>
+          <t>-43,05; 101,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,59; 22,1</t>
+          <t>-77,21; 20,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,38; -14,56</t>
+          <t>-77,35; -17,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 71,79</t>
+          <t>-37,84; 66,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 10,44</t>
+          <t>-68,81; 1,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,16; -28,11</t>
+          <t>-76,05; -31,02</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,6</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,02</t>
+          <t>-1,7; 5,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,59</t>
+          <t>-0,15; 7,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,77</t>
+          <t>1,78; 8,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,65</t>
+          <t>-6,66; 4,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 5,0</t>
+          <t>-5,79; 4,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,88</t>
+          <t>-7,3; 1,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,26</t>
+          <t>-3,11; 3,34</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,92</t>
+          <t>-1,87; 4,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,12</t>
+          <t>-1,86; 4,14</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132,73%</t>
+          <t>131,9%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-23,63%</t>
+          <t>-23,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 218,87</t>
+          <t>-35,47; 226,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 300,51</t>
+          <t>-8,4; 313,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17,44; 364,38</t>
+          <t>26,52; 364,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 43,64</t>
+          <t>-48,25; 48,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 57,57</t>
+          <t>-43,08; 62,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 23,56</t>
+          <t>-52,65; 18,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 53,33</t>
+          <t>-34,85; 58,4</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 80,95</t>
+          <t>-20,8; 76,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 71,16</t>
+          <t>-19,83; 71,09</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,27</t>
+          <t>-3,79; 1,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,46</t>
+          <t>-4,44; 0,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,37</t>
+          <t>-2,19; 3,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,25</t>
+          <t>-3,1; 3,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,67</t>
+          <t>-4,34; 1,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 0,79</t>
+          <t>-3,23; 2,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,42</t>
+          <t>-2,52; 1,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,52</t>
+          <t>-3,49; 0,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,71</t>
+          <t>-1,79; 2,04</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-2,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-28,82%</t>
+          <t>-1,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-17,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 27,16</t>
+          <t>-53,87; 34,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 12,43</t>
+          <t>-60,87; 17,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 55,04</t>
+          <t>-31,03; 68,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 49,37</t>
+          <t>-30,31; 49,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 24,57</t>
+          <t>-42,97; 27,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 9,45</t>
+          <t>-31,45; 38,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 24,42</t>
+          <t>-32,41; 23,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 9,37</t>
+          <t>-42,54; 6,02</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 9,64</t>
+          <t>-22,57; 33,77</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,4</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,26</t>
+          <t>-0,82; 3,38</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,15</t>
+          <t>-0,91; 3,2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,88</t>
+          <t>-2,1; 1,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,63</t>
+          <t>-1,73; 3,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,03</t>
+          <t>-3,17; 1,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,31</t>
+          <t>-4,71; -0,31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,83</t>
+          <t>-0,57; 2,74</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,9</t>
+          <t>-1,35; 1,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,34</t>
+          <t>-2,86; 0,03</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-28,08%</t>
+          <t>-5,39%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-38,43%</t>
+          <t>-39,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-37,25%</t>
+          <t>-28,14%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 125,84</t>
+          <t>-19,5; 125,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 119,73</t>
+          <t>-22,67; 120,18</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 27,68</t>
+          <t>-47,52; 54,52</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 74,19</t>
+          <t>-22,94; 69,93</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 40,13</t>
+          <t>-40,02; 37,97</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-61,08; -5,21</t>
+          <t>-61,35; -4,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 67,11</t>
+          <t>-10,12; 66,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 45,8</t>
+          <t>-23,04; 45,35</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-61,77; -6,61</t>
+          <t>-49,41; 0,94</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,07</t>
+          <t>0,84; 3,12</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,67</t>
+          <t>-0,33; 1,69</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,44</t>
+          <t>0,67; 2,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,51</t>
+          <t>0,87; 3,63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,56</t>
+          <t>-0,91; 1,65</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,21</t>
+          <t>-2,1; 0,38</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,94</t>
+          <t>1,12; 2,94</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,29</t>
+          <t>-0,3; 1,39</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,8</t>
+          <t>-0,33; 1,23</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-19,7%</t>
+          <t>-10,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,64%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>19,09; 86,84</t>
+          <t>17,44; 84,56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 45,19</t>
+          <t>-7,04; 45,94</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 66,86</t>
+          <t>14,11; 77,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10,13; 52,15</t>
+          <t>11,11; 54,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 23,3</t>
+          <t>-11,37; 24,42</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-36,1; -2,96</t>
+          <t>-25,7; 5,75</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,48; 55,9</t>
+          <t>17,64; 53,73</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 23,72</t>
+          <t>-5,09; 25,84</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 14,83</t>
+          <t>-5,07; 23,79</t>
         </is>
       </c>
     </row>
